--- a/data/trans_bre/P1402-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P1402-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-3,02</t>
+          <t>-3,23</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-28,18%</t>
+          <t>-29,2%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 3,57</t>
+          <t>-3,05; 3,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 3,83</t>
+          <t>-5,32; 3,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 2,08</t>
+          <t>-6,27; 1,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 0,87</t>
+          <t>-7,01; 0,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-57,08; 151,26</t>
+          <t>-56,63; 151,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-53,27; 78,56</t>
+          <t>-56,83; 74,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-64,22; 48,54</t>
+          <t>-63,21; 37,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-51,78; 13,0</t>
+          <t>-52,29; 4,12</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 6,34</t>
+          <t>0,17; 6,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 7,78</t>
+          <t>0,21; 7,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 7,11</t>
+          <t>-0,76; 6,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 3,5</t>
+          <t>-3,28; 3,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,78; 165,7</t>
+          <t>0,62; 176,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 147,66</t>
+          <t>1,12; 142,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 115,07</t>
+          <t>-8,84; 113,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,55; 60,47</t>
+          <t>-31,61; 50,45</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,46</t>
+          <t>-1,44</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-13,55%</t>
+          <t>-13,49%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 4,91</t>
+          <t>-2,45; 5,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 5,38</t>
+          <t>-4,56; 5,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 6,43</t>
+          <t>-0,74; 6,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 2,56</t>
+          <t>-5,03; 2,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-33,52; 128,66</t>
+          <t>-35,7; 128,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,28; 71,89</t>
+          <t>-38,05; 69,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 218,15</t>
+          <t>-14,73; 210,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-37,62; 32,33</t>
+          <t>-38,68; 28,9</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,23</t>
+          <t>-1,88</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-36,43%</t>
+          <t>-21,37%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 3,73</t>
+          <t>-2,1; 4,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 5,8</t>
+          <t>-1,73; 6,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,24; -0,78</t>
+          <t>-10,44; -1,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 0,12</t>
+          <t>-5,32; 1,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,47; 112,17</t>
+          <t>-34,82; 142,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,71; 129,52</t>
+          <t>-22,8; 137,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-65,56; -7,18</t>
+          <t>-67,65; -8,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-63,89; 1,75</t>
+          <t>-46,85; 24,56</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,19</t>
+          <t>4,49</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>55,12%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 9,48</t>
+          <t>-0,95; 9,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 9,14</t>
+          <t>-2,49; 9,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 7,56</t>
+          <t>-1,79; 7,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 8,32</t>
+          <t>0,33; 8,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-21,82; 249,82</t>
+          <t>-13,69; 258,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-23,09; 145,03</t>
+          <t>-23,46; 137,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-26,76; 180,35</t>
+          <t>-24,77; 192,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 126,32</t>
+          <t>1,02; 145,3</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-3,87</t>
+          <t>-3,74</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-27,71%</t>
+          <t>-26,73%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 2,73</t>
+          <t>-4,45; 2,64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 7,63</t>
+          <t>-2,18; 7,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 5,15</t>
+          <t>-4,14; 4,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 0,04</t>
+          <t>-8,08; 0,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-67,29; 91,86</t>
+          <t>-63,22; 86,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-21,01; 139,68</t>
+          <t>-22,23; 131,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-41,7; 98,56</t>
+          <t>-49,06; 90,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-47,36; 0,51</t>
+          <t>-48,31; 3,64</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-4,33</t>
+          <t>-2,91</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-47,78%</t>
+          <t>-30,43%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 4,4</t>
+          <t>-1,33; 4,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 3,2</t>
+          <t>-2,74; 3,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 0,86</t>
+          <t>-6,2; 0,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,34; -1,36</t>
+          <t>-5,81; -0,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-19,37; 88,02</t>
+          <t>-18,86; 80,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-28,86; 48,52</t>
+          <t>-28,41; 51,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-47,28; 9,38</t>
+          <t>-46,62; 9,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-75,74; -19,54</t>
+          <t>-48,94; -4,41</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>-1,31</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>-17,03%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 2,52</t>
+          <t>-2,58; 2,51</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 2,08</t>
+          <t>-3,0; 2,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 2,81</t>
+          <t>-3,27; 2,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 4,55</t>
+          <t>-3,52; 0,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-32,46; 48,26</t>
+          <t>-32,32; 48,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-38,15; 42,21</t>
+          <t>-39,29; 40,89</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-29,09; 33,88</t>
+          <t>-29,29; 34,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-28,49; 130,07</t>
+          <t>-39,6; 14,17</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-1,47</t>
+          <t>-1,49</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-16,94%</t>
+          <t>-15,99%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 2,3</t>
+          <t>-0,02; 2,24</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 2,63</t>
+          <t>-0,2; 2,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 1,06</t>
+          <t>-1,69; 1,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 0,49</t>
+          <t>-2,73; -0,4</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 43,93</t>
+          <t>-0,66; 42,91</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 38,0</t>
+          <t>-2,31; 36,97</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-19,57; 13,26</t>
+          <t>-18,16; 16,16</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-33,61; 4,79</t>
+          <t>-26,92; -4,57</t>
         </is>
       </c>
     </row>
